--- a/outputs/59902.xlsx
+++ b/outputs/59902.xlsx
@@ -54,7 +54,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="0"/>
-    <numFmt numFmtId="167" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -475,7 +475,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="9" t="n">
-        <f aca="false">IFERROR(A5-LOOKUP(2,1/($B$4:$B4=B5),$A$4:$A4),0)</f>
+        <f aca="false">IFERROR(A5-INDEX($A$4:$A5,MATCH(B5,$B$4:$B5,0),1),0)</f>
         <v>0</v>
       </c>
       <c r="F5" s="6" t="n">
@@ -497,7 +497,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="9" t="n">
-        <f aca="false">IFERROR(A6-LOOKUP(2,1/($B$4:$B5=B6),$A$4:$A5),0)</f>
+        <f aca="false">IFERROR(A6-INDEX($A$4:$A6,MATCH(B6,$B$4:$B6,0),1),0)</f>
         <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
@@ -519,7 +519,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="9" t="n">
-        <f aca="false">IFERROR(A7-LOOKUP(2,1/($B$4:$B6=B7),$A$4:$A6),0)</f>
+        <f aca="false">IFERROR(A7-INDEX($A$4:$A7,MATCH(B7,$B$4:$B7,0),1),0)</f>
         <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
@@ -541,7 +541,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="9" t="n">
-        <f aca="false">IFERROR(A8-LOOKUP(2,1/($B$4:$B7=B8),$A$4:$A7),0)</f>
+        <f aca="false">IFERROR(A8-INDEX($A$4:$A8,MATCH(B8,$B$4:$B8,0),1),0)</f>
         <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
@@ -563,7 +563,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="9" t="n">
-        <f aca="false">IFERROR(A9-LOOKUP(2,1/($B$4:$B8=B9),$A$4:$A8),0)</f>
+        <f aca="false">IFERROR(A9-INDEX($A$4:$A9,MATCH(B9,$B$4:$B9,0),1),0)</f>
         <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
@@ -585,8 +585,8 @@
         <v>5</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">IFERROR(A10-LOOKUP(2,1/($B$4:$B9=B10),$A$4:$A9),0)</f>
-        <v>1</v>
+        <f aca="false">IFERROR(A10-INDEX($A$4:$A10,MATCH(B10,$B$4:$B10,0),1),0)</f>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>39711</v>
@@ -607,7 +607,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="9" t="n">
-        <f aca="false">IFERROR(A11-LOOKUP(2,1/($B$4:$B10=B11),$A$4:$A10),0)</f>
+        <f aca="false">IFERROR(A11-INDEX($A$4:$A11,MATCH(B11,$B$4:$B11,0),1),0)</f>
         <v>0</v>
       </c>
       <c r="F11" s="6" t="n">
@@ -629,8 +629,8 @@
         <v>7</v>
       </c>
       <c r="C12" s="9" t="n">
-        <f aca="false">IFERROR(A12-LOOKUP(2,1/($B$4:$B11=B12),$A$4:$A11),0)</f>
-        <v>1</v>
+        <f aca="false">IFERROR(A12-INDEX($A$4:$A12,MATCH(B12,$B$4:$B12,0),1),0)</f>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>39710</v>
@@ -651,8 +651,8 @@
         <v>7</v>
       </c>
       <c r="C13" s="9" t="n">
-        <f aca="false">IFERROR(A13-LOOKUP(2,1/($B$4:$B12=B13),$A$4:$A12),0)</f>
-        <v>12</v>
+        <f aca="false">IFERROR(A13-INDEX($A$4:$A13,MATCH(B13,$B$4:$B13,0),1),0)</f>
+        <v>14</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>39705</v>
@@ -673,8 +673,8 @@
         <v>5</v>
       </c>
       <c r="C14" s="9" t="n">
-        <f aca="false">IFERROR(A14-LOOKUP(2,1/($B$4:$B13=B14),$A$4:$A13),0)</f>
-        <v>12</v>
+        <f aca="false">IFERROR(A14-INDEX($A$4:$A14,MATCH(B14,$B$4:$B14,0),1),0)</f>
+        <v>14</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>39705</v>
@@ -695,7 +695,7 @@
         <v>6</v>
       </c>
       <c r="C15" s="9" t="n">
-        <f aca="false">IFERROR(A15-LOOKUP(2,1/($B$4:$B14=B15),$A$4:$A14),0)</f>
+        <f aca="false">IFERROR(A15-INDEX($A$4:$A15,MATCH(B15,$B$4:$B15,0),1),0)</f>
         <v>13</v>
       </c>
       <c r="F15" s="6" t="n">
@@ -717,8 +717,8 @@
         <v>6</v>
       </c>
       <c r="C16" s="9" t="n">
-        <f aca="false">IFERROR(A16-LOOKUP(2,1/($B$4:$B15=B16),$A$4:$A15),0)</f>
-        <v>0</v>
+        <f aca="false">IFERROR(A16-INDEX($A$4:$A16,MATCH(B16,$B$4:$B16,0),1),0)</f>
+        <v>13</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>39705</v>
@@ -739,8 +739,8 @@
         <v>7</v>
       </c>
       <c r="C17" s="9" t="n">
-        <f aca="false">IFERROR(A17-LOOKUP(2,1/($B$4:$B16=B17),$A$4:$A16),0)</f>
-        <v>2</v>
+        <f aca="false">IFERROR(A17-INDEX($A$4:$A17,MATCH(B17,$B$4:$B17,0),1),0)</f>
+        <v>16</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>39704</v>
@@ -761,8 +761,8 @@
         <v>6</v>
       </c>
       <c r="C18" s="9" t="n">
-        <f aca="false">IFERROR(A18-LOOKUP(2,1/($B$4:$B17=B18),$A$4:$A17),0)</f>
-        <v>1</v>
+        <f aca="false">IFERROR(A18-INDEX($A$4:$A18,MATCH(B18,$B$4:$B18,0),1),0)</f>
+        <v>14</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>39704</v>
@@ -783,8 +783,8 @@
         <v>6</v>
       </c>
       <c r="C19" s="9" t="n">
-        <f aca="false">IFERROR(A19-LOOKUP(2,1/($B$4:$B18=B19),$A$4:$A18),0)</f>
-        <v>0</v>
+        <f aca="false">IFERROR(A19-INDEX($A$4:$A19,MATCH(B19,$B$4:$B19,0),1),0)</f>
+        <v>14</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>39703</v>
@@ -805,8 +805,8 @@
         <v>5</v>
       </c>
       <c r="C20" s="9" t="n">
-        <f aca="false">IFERROR(A20-LOOKUP(2,1/($B$4:$B19=B20),$A$4:$A19),0)</f>
-        <v>2</v>
+        <f aca="false">IFERROR(A20-INDEX($A$4:$A20,MATCH(B20,$B$4:$B20,0),1),0)</f>
+        <v>16</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>39703</v>
@@ -827,8 +827,8 @@
         <v>6</v>
       </c>
       <c r="C21" s="9" t="n">
-        <f aca="false">IFERROR(A21-LOOKUP(2,1/($B$4:$B20=B21),$A$4:$A20),0)</f>
-        <v>5</v>
+        <f aca="false">IFERROR(A21-INDEX($A$4:$A21,MATCH(B21,$B$4:$B21,0),1),0)</f>
+        <v>19</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>39691</v>
@@ -849,8 +849,8 @@
         <v>7</v>
       </c>
       <c r="C22" s="9" t="n">
-        <f aca="false">IFERROR(A22-LOOKUP(2,1/($B$4:$B21=B22),$A$4:$A21),0)</f>
-        <v>5</v>
+        <f aca="false">IFERROR(A22-INDEX($A$4:$A22,MATCH(B22,$B$4:$B22,0),1),0)</f>
+        <v>21</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>39691</v>
@@ -871,8 +871,8 @@
         <v>5</v>
       </c>
       <c r="C23" s="9" t="n">
-        <f aca="false">IFERROR(A23-LOOKUP(2,1/($B$4:$B22=B23),$A$4:$A22),0)</f>
-        <v>6</v>
+        <f aca="false">IFERROR(A23-INDEX($A$4:$A23,MATCH(B23,$B$4:$B23,0),1),0)</f>
+        <v>22</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>39691</v>
@@ -893,8 +893,8 @@
         <v>6</v>
       </c>
       <c r="C24" s="9" t="n">
-        <f aca="false">IFERROR(A24-LOOKUP(2,1/($B$4:$B23=B24),$A$4:$A23),0)</f>
-        <v>1</v>
+        <f aca="false">IFERROR(A24-INDEX($A$4:$A24,MATCH(B24,$B$4:$B24,0),1),0)</f>
+        <v>20</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>39691</v>
@@ -915,8 +915,8 @@
         <v>6</v>
       </c>
       <c r="C25" s="9" t="n">
-        <f aca="false">IFERROR(A25-LOOKUP(2,1/($B$4:$B24=B25),$A$4:$A24),0)</f>
-        <v>1</v>
+        <f aca="false">IFERROR(A25-INDEX($A$4:$A25,MATCH(B25,$B$4:$B25,0),1),0)</f>
+        <v>21</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>39690</v>
@@ -937,8 +937,8 @@
         <v>5</v>
       </c>
       <c r="C26" s="9" t="n">
-        <f aca="false">IFERROR(A26-LOOKUP(2,1/($B$4:$B25=B26),$A$4:$A25),0)</f>
-        <v>1</v>
+        <f aca="false">IFERROR(A26-INDEX($A$4:$A26,MATCH(B26,$B$4:$B26,0),1),0)</f>
+        <v>23</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>39690</v>
@@ -959,8 +959,8 @@
         <v>6</v>
       </c>
       <c r="C27" s="9" t="n">
-        <f aca="false">IFERROR(A27-LOOKUP(2,1/($B$4:$B26=B27),$A$4:$A26),0)</f>
-        <v>5</v>
+        <f aca="false">IFERROR(A27-INDEX($A$4:$A27,MATCH(B27,$B$4:$B27,0),1),0)</f>
+        <v>26</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>39689</v>
@@ -981,8 +981,8 @@
         <v>7</v>
       </c>
       <c r="C28" s="9" t="n">
-        <f aca="false">IFERROR(A28-LOOKUP(2,1/($B$4:$B27=B28),$A$4:$A27),0)</f>
-        <v>7</v>
+        <f aca="false">IFERROR(A28-INDEX($A$4:$A28,MATCH(B28,$B$4:$B28,0),1),0)</f>
+        <v>28</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>39689</v>
